--- a/tiflow-diga/develop/1.0.0-draft/StructureDefinition-GEM-ERP-LOG-MedicationDispense-DiGA.xlsx
+++ b/tiflow-diga/develop/1.0.0-draft/StructureDefinition-GEM-ERP-LOG-MedicationDispense-DiGA.xlsx
@@ -326,6 +326,9 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>GEM-ERP-LOG-MedicationDispense-DiGA.prescriptionId</t>
   </si>
   <si>
@@ -431,9 +434,6 @@
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>GEM-ERP-LOG-MedicationDispense-DiGA.angabenZurDiGA.name</t>
@@ -1263,7 +1263,7 @@
         <v>77</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>100</v>
@@ -1272,15 +1272,15 @@
         <v>75</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>83</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1306,10 +1306,10 @@
         <v>86</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1360,7 +1360,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>85</v>
@@ -1375,7 +1375,7 @@
         <v>75</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>75</v>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1409,13 +1409,13 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1466,7 +1466,7 @@
         <v>75</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>85</v>
@@ -1481,7 +1481,7 @@
         <v>75</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>75</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1518,10 +1518,10 @@
         <v>86</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1572,7 +1572,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>85</v>
@@ -1587,7 +1587,7 @@
         <v>75</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>75</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1621,13 +1621,13 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1678,7 +1678,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>85</v>
@@ -1693,7 +1693,7 @@
         <v>75</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>75</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1730,10 +1730,10 @@
         <v>86</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1784,7 +1784,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -1799,7 +1799,7 @@
         <v>75</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>75</v>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1836,10 +1836,10 @@
         <v>86</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1890,7 +1890,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -1905,7 +1905,7 @@
         <v>75</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>75</v>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1939,13 +1939,13 @@
         <v>75</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1996,7 +1996,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -2011,7 +2011,7 @@
         <v>81</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>75</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2125,10 +2125,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2233,14 +2233,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2253,25 +2253,25 @@
         <v>75</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K14" t="s" s="2">
         <v>92</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>95</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>75</v>
@@ -2320,7 +2320,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2329,7 +2329,7 @@
         <v>77</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>100</v>
@@ -2338,7 +2338,7 @@
         <v>75</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>135</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -2581,7 +2581,7 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>143</v>
@@ -2899,7 +2899,7 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>154</v>

--- a/tiflow-diga/develop/1.0.0-draft/StructureDefinition-GEM-ERP-LOG-MedicationDispense-DiGA.xlsx
+++ b/tiflow-diga/develop/1.0.0-draft/StructureDefinition-GEM-ERP-LOG-MedicationDispense-DiGA.xlsx
@@ -326,9 +326,6 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>GEM-ERP-LOG-MedicationDispense-DiGA.prescriptionId</t>
   </si>
   <si>
@@ -434,6 +431,9 @@
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>GEM-ERP-LOG-MedicationDispense-DiGA.angabenZurDiGA.name</t>
@@ -1263,7 +1263,7 @@
         <v>77</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>100</v>
@@ -1272,15 +1272,15 @@
         <v>75</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>101</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1306,10 +1306,10 @@
         <v>86</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1360,7 +1360,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>85</v>
@@ -1375,7 +1375,7 @@
         <v>75</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>75</v>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1409,13 +1409,13 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="L6" t="s" s="2">
-        <v>107</v>
-      </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1466,7 +1466,7 @@
         <v>75</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>85</v>
@@ -1481,7 +1481,7 @@
         <v>75</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>75</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1518,10 +1518,10 @@
         <v>86</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1572,7 +1572,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>85</v>
@@ -1587,7 +1587,7 @@
         <v>75</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>75</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1621,13 +1621,13 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="L8" t="s" s="2">
-        <v>114</v>
-      </c>
       <c r="M8" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1678,7 +1678,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>85</v>
@@ -1693,7 +1693,7 @@
         <v>75</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>75</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1730,10 +1730,10 @@
         <v>86</v>
       </c>
       <c r="L9" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1784,7 +1784,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -1799,7 +1799,7 @@
         <v>75</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>75</v>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1836,10 +1836,10 @@
         <v>86</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1890,7 +1890,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -1905,7 +1905,7 @@
         <v>75</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>75</v>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1939,13 +1939,13 @@
         <v>75</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="L11" t="s" s="2">
-        <v>125</v>
-      </c>
       <c r="M11" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1996,7 +1996,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -2011,7 +2011,7 @@
         <v>81</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>75</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2125,10 +2125,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2233,14 +2233,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2253,25 +2253,25 @@
         <v>75</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K14" t="s" s="2">
         <v>92</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>95</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>75</v>
@@ -2320,7 +2320,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2329,7 +2329,7 @@
         <v>77</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>100</v>
@@ -2338,7 +2338,7 @@
         <v>75</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>101</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -2581,7 +2581,7 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>143</v>
@@ -2899,7 +2899,7 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>154</v>
